--- a/Codex Wheat.xlsx
+++ b/Codex Wheat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Myburgh Swiegers\Projects\Codex_GDI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA244329-3DEC-4A99-AC66-8952E2F7C4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53EC4FA7-EB9E-4BF5-8E90-DA3E06D13CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="16080" windowWidth="29040" windowHeight="15840" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="-28980" yWindow="0" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Wheat" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="424">
   <si>
     <t>2024/25</t>
   </si>
@@ -1302,6 +1302,12 @@
   </si>
   <si>
     <t>04/07 - 10/07/2026</t>
+  </si>
+  <si>
+    <t>11/07 - 17/07/2026</t>
+  </si>
+  <si>
+    <t>18/07 - 24/07/2026</t>
   </si>
 </sst>
 </file>
@@ -1357,7 +1363,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1370,8 +1376,20 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1435,6 +1453,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0A0101"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF0A0101"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color rgb="FF0A0101"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0A0101"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF0A0101"/>
+      </right>
+      <top style="dotted">
+        <color rgb="FF0A0101"/>
+      </top>
+      <bottom style="dotted">
+        <color rgb="FF0A0101"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0A0101"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF0A0101"/>
+      </right>
+      <top style="dotted">
+        <color rgb="FF0A0101"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0A0101"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1442,7 +1503,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1468,6 +1529,17 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1751,7 +1823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:N407"/>
+  <dimension ref="A1:N409"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -9132,22 +9204,22 @@
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A366" s="1">
+      <c r="A366" s="13">
         <v>52</v>
       </c>
-      <c r="B366" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C366" s="4" t="s">
+      <c r="B366" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C366" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="D366" s="6">
+      <c r="D366" s="15">
         <v>1021</v>
       </c>
-      <c r="E366" s="6">
+      <c r="E366" s="15">
         <v>1503</v>
       </c>
-      <c r="F366" s="6">
+      <c r="F366" s="15">
         <v>2524</v>
       </c>
     </row>
@@ -9158,16 +9230,16 @@
       <c r="B367" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C367" s="4" t="s">
+      <c r="C367" s="16" t="s">
         <v>391</v>
       </c>
-      <c r="D367" s="6">
+      <c r="D367" s="17">
         <v>2616</v>
       </c>
-      <c r="E367" s="6">
+      <c r="E367" s="17">
         <v>-262</v>
       </c>
-      <c r="F367" s="6">
+      <c r="F367" s="17">
         <v>2354</v>
       </c>
     </row>
@@ -9178,16 +9250,16 @@
       <c r="B368" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C368" s="4" t="s">
+      <c r="C368" s="18" t="s">
         <v>392</v>
       </c>
-      <c r="D368" s="6">
+      <c r="D368" s="19">
         <v>13396</v>
       </c>
-      <c r="E368" s="6">
+      <c r="E368" s="19">
         <v>-166</v>
       </c>
-      <c r="F368" s="6">
+      <c r="F368" s="19">
         <v>13230</v>
       </c>
     </row>
@@ -9198,16 +9270,16 @@
       <c r="B369" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C369" s="4" t="s">
+      <c r="C369" s="18" t="s">
         <v>393</v>
       </c>
-      <c r="D369" s="6">
+      <c r="D369" s="19">
         <v>29408</v>
       </c>
-      <c r="E369" s="6">
+      <c r="E369" s="19">
         <v>-4713</v>
       </c>
-      <c r="F369" s="6">
+      <c r="F369" s="19">
         <v>24695</v>
       </c>
     </row>
@@ -9218,16 +9290,16 @@
       <c r="B370" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C370" s="4" t="s">
+      <c r="C370" s="18" t="s">
         <v>394</v>
       </c>
-      <c r="D370" s="6">
+      <c r="D370" s="19">
         <v>157335</v>
       </c>
-      <c r="E370" s="6">
+      <c r="E370" s="19">
         <v>184</v>
       </c>
-      <c r="F370" s="6">
+      <c r="F370" s="19">
         <v>157519</v>
       </c>
     </row>
@@ -9238,16 +9310,16 @@
       <c r="B371" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C371" s="4" t="s">
+      <c r="C371" s="18" t="s">
         <v>395</v>
       </c>
-      <c r="D371" s="6">
+      <c r="D371" s="19">
         <v>222435</v>
       </c>
-      <c r="E371" s="6">
+      <c r="E371" s="19">
         <v>499</v>
       </c>
-      <c r="F371" s="6">
+      <c r="F371" s="19">
         <v>222934</v>
       </c>
     </row>
@@ -9258,16 +9330,16 @@
       <c r="B372" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C372" s="4" t="s">
+      <c r="C372" s="18" t="s">
         <v>396</v>
       </c>
-      <c r="D372" s="6">
+      <c r="D372" s="19">
         <v>228945</v>
       </c>
-      <c r="E372" s="6">
+      <c r="E372" s="19">
         <v>358</v>
       </c>
-      <c r="F372" s="6">
+      <c r="F372" s="19">
         <v>229303</v>
       </c>
     </row>
@@ -9278,16 +9350,16 @@
       <c r="B373" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C373" s="4" t="s">
+      <c r="C373" s="18" t="s">
         <v>397</v>
       </c>
-      <c r="D373" s="6">
+      <c r="D373" s="19">
         <v>186653</v>
       </c>
-      <c r="E373" s="6">
+      <c r="E373" s="19">
         <v>143</v>
       </c>
-      <c r="F373" s="6">
+      <c r="F373" s="19">
         <v>186796</v>
       </c>
     </row>
@@ -9298,16 +9370,16 @@
       <c r="B374" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C374" s="4" t="s">
+      <c r="C374" s="18" t="s">
         <v>398</v>
       </c>
-      <c r="D374" s="6">
+      <c r="D374" s="19">
         <v>124491</v>
       </c>
-      <c r="E374" s="6">
+      <c r="E374" s="19">
         <v>1761</v>
       </c>
-      <c r="F374" s="6">
+      <c r="F374" s="19">
         <v>126252</v>
       </c>
     </row>
@@ -9318,16 +9390,16 @@
       <c r="B375" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C375" s="4" t="s">
+      <c r="C375" s="18" t="s">
         <v>399</v>
       </c>
-      <c r="D375" s="6">
+      <c r="D375" s="19">
         <v>152930</v>
       </c>
-      <c r="E375" s="6">
+      <c r="E375" s="19">
         <v>7166</v>
       </c>
-      <c r="F375" s="6">
+      <c r="F375" s="19">
         <v>160096</v>
       </c>
     </row>
@@ -9338,16 +9410,16 @@
       <c r="B376" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C376" s="4" t="s">
+      <c r="C376" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="D376" s="6">
+      <c r="D376" s="19">
         <v>212513</v>
       </c>
-      <c r="E376" s="6">
+      <c r="E376" s="19">
         <v>8868</v>
       </c>
-      <c r="F376" s="6">
+      <c r="F376" s="19">
         <v>221381</v>
       </c>
     </row>
@@ -9358,16 +9430,16 @@
       <c r="B377" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C377" s="4" t="s">
+      <c r="C377" s="18" t="s">
         <v>401</v>
       </c>
-      <c r="D377" s="6">
+      <c r="D377" s="19">
         <v>164292</v>
       </c>
-      <c r="E377" s="6">
+      <c r="E377" s="19">
         <v>6607</v>
       </c>
-      <c r="F377" s="6">
+      <c r="F377" s="19">
         <v>170899</v>
       </c>
     </row>
@@ -9378,16 +9450,16 @@
       <c r="B378" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C378" s="4" t="s">
+      <c r="C378" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="D378" s="6">
+      <c r="D378" s="19">
         <v>42591</v>
       </c>
-      <c r="E378" s="6">
+      <c r="E378" s="19">
         <v>3391</v>
       </c>
-      <c r="F378" s="6">
+      <c r="F378" s="19">
         <v>45982</v>
       </c>
     </row>
@@ -9398,16 +9470,16 @@
       <c r="B379" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C379" s="4" t="s">
+      <c r="C379" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="D379" s="6">
+      <c r="D379" s="19">
         <v>12392</v>
       </c>
-      <c r="E379" s="6">
+      <c r="E379" s="19">
         <v>676</v>
       </c>
-      <c r="F379" s="6">
+      <c r="F379" s="19">
         <v>13068</v>
       </c>
     </row>
@@ -9418,16 +9490,16 @@
       <c r="B380" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C380" s="4" t="s">
+      <c r="C380" s="18" t="s">
         <v>404</v>
       </c>
-      <c r="D380" s="6">
+      <c r="D380" s="19">
         <v>18336</v>
       </c>
-      <c r="E380" s="6">
+      <c r="E380" s="19">
         <v>1293</v>
       </c>
-      <c r="F380" s="6">
+      <c r="F380" s="19">
         <v>19629</v>
       </c>
     </row>
@@ -9438,16 +9510,16 @@
       <c r="B381" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C381" s="4" t="s">
+      <c r="C381" s="18" t="s">
         <v>405</v>
       </c>
-      <c r="D381" s="6">
+      <c r="D381" s="19">
         <v>25231</v>
       </c>
-      <c r="E381" s="6">
+      <c r="E381" s="19">
         <v>5801</v>
       </c>
-      <c r="F381" s="6">
+      <c r="F381" s="19">
         <v>31032</v>
       </c>
     </row>
@@ -9458,16 +9530,16 @@
       <c r="B382" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C382" s="4" t="s">
+      <c r="C382" s="18" t="s">
         <v>406</v>
       </c>
-      <c r="D382" s="6">
+      <c r="D382" s="19">
         <v>18926</v>
       </c>
-      <c r="E382" s="6">
+      <c r="E382" s="19">
         <v>7890</v>
       </c>
-      <c r="F382" s="6">
+      <c r="F382" s="19">
         <v>26816</v>
       </c>
     </row>
@@ -9478,16 +9550,16 @@
       <c r="B383" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C383" s="4" t="s">
+      <c r="C383" s="18" t="s">
         <v>407</v>
       </c>
-      <c r="D383" s="6">
+      <c r="D383" s="19">
         <v>15156</v>
       </c>
-      <c r="E383" s="6">
+      <c r="E383" s="19">
         <v>6777</v>
       </c>
-      <c r="F383" s="6">
+      <c r="F383" s="19">
         <v>21933</v>
       </c>
     </row>
@@ -9498,16 +9570,16 @@
       <c r="B384" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C384" s="4" t="s">
+      <c r="C384" s="18" t="s">
         <v>408</v>
       </c>
-      <c r="D384" s="6">
+      <c r="D384" s="19">
         <v>16903</v>
       </c>
-      <c r="E384" s="6">
+      <c r="E384" s="19">
         <v>3714</v>
       </c>
-      <c r="F384" s="6">
+      <c r="F384" s="19">
         <v>20617</v>
       </c>
     </row>
@@ -9518,16 +9590,16 @@
       <c r="B385" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C385" s="4" t="s">
+      <c r="C385" s="18" t="s">
         <v>409</v>
       </c>
-      <c r="D385" s="6">
+      <c r="D385" s="19">
         <v>11023</v>
       </c>
-      <c r="E385" s="6">
+      <c r="E385" s="19">
         <v>5192</v>
       </c>
-      <c r="F385" s="6">
+      <c r="F385" s="19">
         <v>16215</v>
       </c>
     </row>
@@ -9538,16 +9610,16 @@
       <c r="B386" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C386" s="4" t="s">
+      <c r="C386" s="18" t="s">
         <v>410</v>
       </c>
-      <c r="D386" s="6">
+      <c r="D386" s="19">
         <v>6314</v>
       </c>
-      <c r="E386" s="6">
+      <c r="E386" s="19">
         <v>3971</v>
       </c>
-      <c r="F386" s="6">
+      <c r="F386" s="19">
         <v>10285</v>
       </c>
     </row>
@@ -9558,16 +9630,16 @@
       <c r="B387" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C387" s="4" t="s">
+      <c r="C387" s="18" t="s">
         <v>411</v>
       </c>
-      <c r="D387" s="6">
+      <c r="D387" s="19">
         <v>6696</v>
       </c>
-      <c r="E387" s="6">
+      <c r="E387" s="19">
         <v>4601</v>
       </c>
-      <c r="F387" s="6">
+      <c r="F387" s="19">
         <v>11297</v>
       </c>
     </row>
@@ -9578,16 +9650,16 @@
       <c r="B388" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C388" s="4" t="s">
+      <c r="C388" s="18" t="s">
         <v>412</v>
       </c>
-      <c r="D388" s="6">
+      <c r="D388" s="19">
         <v>5265</v>
       </c>
-      <c r="E388" s="6">
+      <c r="E388" s="19">
         <v>3075</v>
       </c>
-      <c r="F388" s="6">
+      <c r="F388" s="19">
         <v>8340</v>
       </c>
     </row>
@@ -9598,17 +9670,17 @@
       <c r="B389" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C389" s="4" t="s">
+      <c r="C389" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D389" s="6">
+      <c r="D389" s="19">
         <v>8092</v>
       </c>
-      <c r="E389" s="6">
-        <v>5362</v>
-      </c>
-      <c r="F389" s="6">
-        <v>13454</v>
+      <c r="E389" s="19">
+        <v>5291</v>
+      </c>
+      <c r="F389" s="19">
+        <v>13383</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -9618,16 +9690,16 @@
       <c r="B390" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C390" s="4" t="s">
+      <c r="C390" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D390" s="6">
+      <c r="D390" s="19">
         <v>10258</v>
       </c>
-      <c r="E390" s="6">
+      <c r="E390" s="19">
         <v>3379</v>
       </c>
-      <c r="F390" s="6">
+      <c r="F390" s="19">
         <v>13637</v>
       </c>
     </row>
@@ -9638,16 +9710,16 @@
       <c r="B391" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C391" s="4" t="s">
+      <c r="C391" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D391" s="6">
+      <c r="D391" s="19">
         <v>12856</v>
       </c>
-      <c r="E391" s="6">
+      <c r="E391" s="19">
         <v>1206</v>
       </c>
-      <c r="F391" s="6">
+      <c r="F391" s="19">
         <v>14062</v>
       </c>
     </row>
@@ -9658,16 +9730,16 @@
       <c r="B392" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C392" s="4" t="s">
+      <c r="C392" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D392" s="6">
+      <c r="D392" s="19">
         <v>9436</v>
       </c>
-      <c r="E392" s="6">
+      <c r="E392" s="19">
         <v>1888</v>
       </c>
-      <c r="F392" s="6">
+      <c r="F392" s="19">
         <v>11324</v>
       </c>
     </row>
@@ -9678,16 +9750,16 @@
       <c r="B393" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C393" s="4" t="s">
+      <c r="C393" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D393" s="6">
+      <c r="D393" s="19">
         <v>4255</v>
       </c>
-      <c r="E393" s="6">
+      <c r="E393" s="19">
         <v>557</v>
       </c>
-      <c r="F393" s="6">
+      <c r="F393" s="19">
         <v>4812</v>
       </c>
     </row>
@@ -9698,16 +9770,16 @@
       <c r="B394" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C394" s="4" t="s">
+      <c r="C394" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D394" s="6">
+      <c r="D394" s="19">
         <v>5394</v>
       </c>
-      <c r="E394" s="6">
+      <c r="E394" s="19">
         <v>1551</v>
       </c>
-      <c r="F394" s="6">
+      <c r="F394" s="19">
         <v>6945</v>
       </c>
     </row>
@@ -9718,17 +9790,17 @@
       <c r="B395" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C395" s="4" t="s">
+      <c r="C395" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D395" s="6">
+      <c r="D395" s="19">
         <v>5325</v>
       </c>
-      <c r="E395" s="6">
-        <v>1347</v>
-      </c>
-      <c r="F395" s="6">
-        <v>6672</v>
+      <c r="E395" s="19">
+        <v>1023</v>
+      </c>
+      <c r="F395" s="19">
+        <v>6348</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -9738,17 +9810,17 @@
       <c r="B396" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C396" s="4" t="s">
+      <c r="C396" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D396" s="6">
+      <c r="D396" s="19">
         <v>5065</v>
       </c>
-      <c r="E396" s="6">
-        <v>3694</v>
-      </c>
-      <c r="F396" s="6">
-        <v>8759</v>
+      <c r="E396" s="19">
+        <v>3406</v>
+      </c>
+      <c r="F396" s="19">
+        <v>8471</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -9758,16 +9830,16 @@
       <c r="B397" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C397" s="4" t="s">
+      <c r="C397" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D397" s="6">
+      <c r="D397" s="19">
         <v>2322</v>
       </c>
-      <c r="E397" s="6">
+      <c r="E397" s="19">
         <v>2271</v>
       </c>
-      <c r="F397" s="6">
+      <c r="F397" s="19">
         <v>4593</v>
       </c>
     </row>
@@ -9778,16 +9850,16 @@
       <c r="B398" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C398" s="4" t="s">
+      <c r="C398" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D398" s="6">
+      <c r="D398" s="19">
         <v>862</v>
       </c>
-      <c r="E398" s="6">
+      <c r="E398" s="19">
         <v>1168</v>
       </c>
-      <c r="F398" s="6">
+      <c r="F398" s="19">
         <v>2030</v>
       </c>
     </row>
@@ -9798,16 +9870,16 @@
       <c r="B399" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C399" s="4" t="s">
+      <c r="C399" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D399" s="6">
+      <c r="D399" s="19">
         <v>741</v>
       </c>
-      <c r="E399" s="6">
+      <c r="E399" s="19">
         <v>645</v>
       </c>
-      <c r="F399" s="6">
+      <c r="F399" s="19">
         <v>1386</v>
       </c>
     </row>
@@ -9818,16 +9890,16 @@
       <c r="B400" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C400" s="4" t="s">
+      <c r="C400" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D400" s="6">
+      <c r="D400" s="19">
         <v>1791</v>
       </c>
-      <c r="E400" s="6">
+      <c r="E400" s="19">
         <v>397</v>
       </c>
-      <c r="F400" s="6">
+      <c r="F400" s="19">
         <v>2188</v>
       </c>
     </row>
@@ -9838,16 +9910,16 @@
       <c r="B401" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C401" s="4" t="s">
+      <c r="C401" s="18" t="s">
         <v>414</v>
       </c>
-      <c r="D401" s="6">
+      <c r="D401" s="19">
         <v>586</v>
       </c>
-      <c r="E401" s="6">
+      <c r="E401" s="19">
         <v>724</v>
       </c>
-      <c r="F401" s="6">
+      <c r="F401" s="19">
         <v>1310</v>
       </c>
     </row>
@@ -9858,17 +9930,17 @@
       <c r="B402" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C402" s="4" t="s">
+      <c r="C402" s="18" t="s">
         <v>415</v>
       </c>
-      <c r="D402" s="6">
+      <c r="D402" s="19">
         <v>1710</v>
       </c>
-      <c r="E402" s="6">
-        <v>0</v>
-      </c>
-      <c r="F402" s="6">
-        <v>1710</v>
+      <c r="E402" s="19">
+        <v>147</v>
+      </c>
+      <c r="F402" s="19">
+        <v>1857</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -9878,17 +9950,17 @@
       <c r="B403" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C403" s="4" t="s">
+      <c r="C403" s="18" t="s">
         <v>416</v>
       </c>
-      <c r="D403" s="6">
+      <c r="D403" s="19">
         <v>785</v>
       </c>
-      <c r="E403" s="6">
-        <v>0</v>
-      </c>
-      <c r="F403" s="6">
-        <v>785</v>
+      <c r="E403" s="19">
+        <v>501</v>
+      </c>
+      <c r="F403" s="19">
+        <v>1286</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -9898,17 +9970,17 @@
       <c r="B404" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C404" s="4" t="s">
+      <c r="C404" s="18" t="s">
         <v>417</v>
       </c>
-      <c r="D404" s="6">
+      <c r="D404" s="19">
         <v>1695</v>
       </c>
-      <c r="E404" s="6">
-        <v>0</v>
-      </c>
-      <c r="F404" s="6">
-        <v>1695</v>
+      <c r="E404" s="19">
+        <v>-62</v>
+      </c>
+      <c r="F404" s="19">
+        <v>1633</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -9918,17 +9990,17 @@
       <c r="B405" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C405" s="4" t="s">
+      <c r="C405" s="18" t="s">
         <v>418</v>
       </c>
-      <c r="D405" s="6">
+      <c r="D405" s="19">
         <v>831</v>
       </c>
-      <c r="E405" s="6">
-        <v>305</v>
-      </c>
-      <c r="F405" s="6">
-        <v>1136</v>
+      <c r="E405" s="19">
+        <v>1295</v>
+      </c>
+      <c r="F405" s="19">
+        <v>2126</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -9938,16 +10010,16 @@
       <c r="B406" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C406" s="4" t="s">
+      <c r="C406" s="18" t="s">
         <v>419</v>
       </c>
-      <c r="D406" s="6">
+      <c r="D406" s="19">
         <v>556</v>
       </c>
-      <c r="E406" s="6">
-        <v>0</v>
-      </c>
-      <c r="F406" s="6">
+      <c r="E406" s="19">
+        <v>0</v>
+      </c>
+      <c r="F406" s="19">
         <v>556</v>
       </c>
     </row>
@@ -9958,17 +10030,57 @@
       <c r="B407" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C407" s="4" t="s">
+      <c r="C407" s="18" t="s">
         <v>421</v>
       </c>
-      <c r="D407" s="6">
+      <c r="D407" s="19">
         <v>389</v>
       </c>
-      <c r="E407" s="6">
-        <v>0</v>
-      </c>
-      <c r="F407" s="6">
-        <v>389</v>
+      <c r="E407" s="19">
+        <v>-59</v>
+      </c>
+      <c r="F407" s="19">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A408" s="1">
+        <v>42</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C408" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="D408" s="19">
+        <v>730</v>
+      </c>
+      <c r="E408" s="19">
+        <v>0</v>
+      </c>
+      <c r="F408" s="19">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A409" s="1">
+        <v>43</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C409" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="D409" s="21">
+        <v>729</v>
+      </c>
+      <c r="E409" s="21">
+        <v>0</v>
+      </c>
+      <c r="F409" s="21">
+        <v>729</v>
       </c>
     </row>
   </sheetData>
@@ -9978,6 +10090,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075ECE796D7EABA42BC0DB2CA73C7CE00" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e2ecee1b3d34a959aed38d5dc4c878f4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8" xmlns:ns3="ae149517-eeaa-465d-b3b6-396a1e23bc6e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9af26d9f7c79c0f2a842447557dfee25" ns2:_="" ns3:_="">
     <xsd:import namespace="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
@@ -10204,27 +10336,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
+    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409921FC-0447-4F0C-872E-CE24E2C3DE02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10241,23 +10372,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
-    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Codex Wheat.xlsx
+++ b/Codex Wheat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53EC4FA7-EB9E-4BF5-8E90-DA3E06D13CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11027E43-DCDC-45A3-96A8-8670555A9D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28980" yWindow="0" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="-28920" yWindow="-16200" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Wheat" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="425">
   <si>
     <t>2024/25</t>
   </si>
@@ -1308,6 +1308,9 @@
   </si>
   <si>
     <t>18/07 - 24/07/2026</t>
+  </si>
+  <si>
+    <t>25/07 - 31/07/2026</t>
   </si>
 </sst>
 </file>
@@ -1823,7 +1826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:N409"/>
+  <dimension ref="A1:N410"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10070,17 +10073,37 @@
       <c r="B409" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C409" s="20" t="s">
+      <c r="C409" s="18" t="s">
         <v>423</v>
       </c>
-      <c r="D409" s="21">
+      <c r="D409" s="19">
         <v>729</v>
       </c>
-      <c r="E409" s="21">
-        <v>0</v>
-      </c>
-      <c r="F409" s="21">
+      <c r="E409" s="19">
+        <v>0</v>
+      </c>
+      <c r="F409" s="19">
         <v>729</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A410" s="1">
+        <v>44</v>
+      </c>
+      <c r="B410" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C410" s="20" t="s">
+        <v>424</v>
+      </c>
+      <c r="D410" s="21">
+        <v>537</v>
+      </c>
+      <c r="E410" s="21">
+        <v>0</v>
+      </c>
+      <c r="F410" s="21">
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -10101,15 +10124,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075ECE796D7EABA42BC0DB2CA73C7CE00" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e2ecee1b3d34a959aed38d5dc4c878f4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8" xmlns:ns3="ae149517-eeaa-465d-b3b6-396a1e23bc6e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9af26d9f7c79c0f2a842447557dfee25" ns2:_="" ns3:_="">
     <xsd:import namespace="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
@@ -10336,6 +10350,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
   <ds:schemaRefs>
@@ -10348,14 +10371,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409921FC-0447-4F0C-872E-CE24E2C3DE02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10372,4 +10387,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Codex Wheat.xlsx
+++ b/Codex Wheat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11027E43-DCDC-45A3-96A8-8670555A9D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FA2D21-D476-4BC5-B4C9-E186C3470415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-16200" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="426">
   <si>
     <t>2024/25</t>
   </si>
@@ -1311,6 +1311,9 @@
   </si>
   <si>
     <t>25/07 - 31/07/2026</t>
+  </si>
+  <si>
+    <t>01/08 - 07/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1826,7 +1829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:N410"/>
+  <dimension ref="A1:N411"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10093,17 +10096,37 @@
       <c r="B410" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C410" s="20" t="s">
+      <c r="C410" s="18" t="s">
         <v>424</v>
       </c>
-      <c r="D410" s="21">
+      <c r="D410" s="19">
         <v>537</v>
       </c>
-      <c r="E410" s="21">
-        <v>0</v>
-      </c>
-      <c r="F410" s="21">
-        <v>537</v>
+      <c r="E410" s="19">
+        <v>62</v>
+      </c>
+      <c r="F410" s="19">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A411" s="1">
+        <v>45</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C411" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="D411" s="21">
+        <v>811</v>
+      </c>
+      <c r="E411" s="21">
+        <v>0</v>
+      </c>
+      <c r="F411" s="21">
+        <v>811</v>
       </c>
     </row>
   </sheetData>
@@ -10124,6 +10147,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075ECE796D7EABA42BC0DB2CA73C7CE00" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e2ecee1b3d34a959aed38d5dc4c878f4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8" xmlns:ns3="ae149517-eeaa-465d-b3b6-396a1e23bc6e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9af26d9f7c79c0f2a842447557dfee25" ns2:_="" ns3:_="">
     <xsd:import namespace="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
@@ -10350,15 +10382,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
   <ds:schemaRefs>
@@ -10371,6 +10394,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409921FC-0447-4F0C-872E-CE24E2C3DE02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10387,12 +10418,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Codex Wheat.xlsx
+++ b/Codex Wheat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FA2D21-D476-4BC5-B4C9-E186C3470415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B96306-26DC-43C7-80F7-FBBA9E226843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-16200" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="-120" yWindow="-16335" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Wheat" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="427">
   <si>
     <t>2024/25</t>
   </si>
@@ -1314,6 +1314,9 @@
   </si>
   <si>
     <t>01/08 - 07/08/2026</t>
+  </si>
+  <si>
+    <t>08/08 - 14/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1829,7 +1832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:N411"/>
+  <dimension ref="A1:N412"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10116,17 +10119,37 @@
       <c r="B411" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C411" s="20" t="s">
+      <c r="C411" s="18" t="s">
         <v>425</v>
       </c>
-      <c r="D411" s="21">
+      <c r="D411" s="19">
         <v>811</v>
       </c>
-      <c r="E411" s="21">
-        <v>0</v>
-      </c>
-      <c r="F411" s="21">
+      <c r="E411" s="19">
+        <v>0</v>
+      </c>
+      <c r="F411" s="19">
         <v>811</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A412" s="1">
+        <v>46</v>
+      </c>
+      <c r="B412" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C412" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="D412" s="21">
+        <v>1090</v>
+      </c>
+      <c r="E412" s="21">
+        <v>0</v>
+      </c>
+      <c r="F412" s="21">
+        <v>1090</v>
       </c>
     </row>
   </sheetData>
@@ -10147,15 +10170,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075ECE796D7EABA42BC0DB2CA73C7CE00" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e2ecee1b3d34a959aed38d5dc4c878f4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8" xmlns:ns3="ae149517-eeaa-465d-b3b6-396a1e23bc6e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9af26d9f7c79c0f2a842447557dfee25" ns2:_="" ns3:_="">
     <xsd:import namespace="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
@@ -10382,6 +10396,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
   <ds:schemaRefs>
@@ -10394,14 +10417,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409921FC-0447-4F0C-872E-CE24E2C3DE02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10418,4 +10433,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Codex Wheat.xlsx
+++ b/Codex Wheat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B96306-26DC-43C7-80F7-FBBA9E226843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1A2C3F-991D-4ED6-8050-3A826960624F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16335" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="428">
   <si>
     <t>2024/25</t>
   </si>
@@ -1317,6 +1317,9 @@
   </si>
   <si>
     <t>08/08 - 14/08/2026</t>
+  </si>
+  <si>
+    <t>15/08 - 21/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1832,7 +1835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:N412"/>
+  <dimension ref="A1:N413"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -9946,10 +9949,10 @@
         <v>1710</v>
       </c>
       <c r="E402" s="19">
-        <v>147</v>
+        <v>6</v>
       </c>
       <c r="F402" s="19">
-        <v>1857</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -10006,10 +10009,10 @@
         <v>831</v>
       </c>
       <c r="E405" s="19">
-        <v>1295</v>
+        <v>1366</v>
       </c>
       <c r="F405" s="19">
-        <v>2126</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -10026,10 +10029,10 @@
         <v>556</v>
       </c>
       <c r="E406" s="19">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F406" s="19">
-        <v>556</v>
+        <v>584</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -10046,10 +10049,10 @@
         <v>389</v>
       </c>
       <c r="E407" s="19">
-        <v>-59</v>
+        <v>267</v>
       </c>
       <c r="F407" s="19">
-        <v>330</v>
+        <v>656</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -10066,10 +10069,10 @@
         <v>730</v>
       </c>
       <c r="E408" s="19">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="F408" s="19">
-        <v>730</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -10086,10 +10089,10 @@
         <v>729</v>
       </c>
       <c r="E409" s="19">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F409" s="19">
-        <v>729</v>
+        <v>801</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -10106,10 +10109,10 @@
         <v>537</v>
       </c>
       <c r="E410" s="19">
-        <v>62</v>
+        <v>631</v>
       </c>
       <c r="F410" s="19">
-        <v>599</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -10139,17 +10142,37 @@
       <c r="B412" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C412" s="20" t="s">
+      <c r="C412" s="18" t="s">
         <v>426</v>
       </c>
-      <c r="D412" s="21">
+      <c r="D412" s="19">
         <v>1090</v>
       </c>
-      <c r="E412" s="21">
-        <v>0</v>
-      </c>
-      <c r="F412" s="21">
+      <c r="E412" s="19">
+        <v>0</v>
+      </c>
+      <c r="F412" s="19">
         <v>1090</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A413" s="1">
+        <v>47</v>
+      </c>
+      <c r="B413" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C413" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="D413" s="21">
+        <v>1100</v>
+      </c>
+      <c r="E413" s="21">
+        <v>0</v>
+      </c>
+      <c r="F413" s="21">
+        <v>1100</v>
       </c>
     </row>
   </sheetData>
@@ -10159,14 +10182,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10397,21 +10418,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
-    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10436,9 +10456,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
+    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Codex Wheat.xlsx
+++ b/Codex Wheat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1A2C3F-991D-4ED6-8050-3A826960624F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF3EE52-676B-454E-9CB8-417357F316CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16335" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="-28980" yWindow="0" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Wheat" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="429">
   <si>
     <t>2024/25</t>
   </si>
@@ -1320,6 +1320,9 @@
   </si>
   <si>
     <t>15/08 - 21/08/2026</t>
+  </si>
+  <si>
+    <t>22/08 - 28/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1835,7 +1838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:N413"/>
+  <dimension ref="A1:N414"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10162,17 +10165,37 @@
       <c r="B413" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C413" s="20" t="s">
+      <c r="C413" s="18" t="s">
         <v>427</v>
       </c>
-      <c r="D413" s="21">
+      <c r="D413" s="19">
         <v>1100</v>
       </c>
-      <c r="E413" s="21">
-        <v>0</v>
-      </c>
-      <c r="F413" s="21">
+      <c r="E413" s="19">
+        <v>0</v>
+      </c>
+      <c r="F413" s="19">
         <v>1100</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A414" s="1">
+        <v>48</v>
+      </c>
+      <c r="B414" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C414" s="20" t="s">
+        <v>428</v>
+      </c>
+      <c r="D414" s="21">
+        <v>1030</v>
+      </c>
+      <c r="E414" s="21">
+        <v>0</v>
+      </c>
+      <c r="F414" s="21">
+        <v>1030</v>
       </c>
     </row>
   </sheetData>
@@ -10182,12 +10205,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10418,20 +10443,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
+    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10456,12 +10482,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
-    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>